--- a/sources/ling_step6.xlsx
+++ b/sources/ling_step6.xlsx
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Fire Cracker - [Roll up or down]</t>
+          <t>Fire Cracker [Roll up or down]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">

--- a/sources/ling_step6.xlsx
+++ b/sources/ling_step6.xlsx
@@ -893,6 +893,11 @@
           <t>Which throw is done depends on the position. Use the proper escape command depending on the throw.</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>a24bf04e-0d2e-4145-8a90-082242d8b227</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>a24bf04e-0d2e-4145-8a90-082242d8b227</t>
@@ -940,6 +945,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>50a70a48-afe6-40fd-8f35-16ca8bff01a0</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>50a70a48-afe6-40fd-8f35-16ca8bff01a0</t>
@@ -987,6 +997,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>4907eee5-3efc-44a2-a055-d184d67b1678</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>4907eee5-3efc-44a2-a055-d184d67b1678</t>
@@ -1032,6 +1047,11 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>cb6c831f-06d3-4000-b9f7-9fd513e65128</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -8097,6 +8117,11 @@
           <t>mhhmmMLLmm</t>
         </is>
       </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>d6eeaf40-1498-4551-b18c-5d04a4263947</t>
+        </is>
+      </c>
       <c r="Q149" t="inlineStr">
         <is>
           <t>d6eeaf40-1498-4551-b18c-5d04a4263947</t>
@@ -8127,6 +8152,11 @@
       <c r="K150" t="inlineStr">
         <is>
           <t>mhhLLmmllmm</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>a77680ba-55cb-467b-b7b3-7b9a5ced7ee7</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
